--- a/Outputs/PtX_demand_LU.xlsx
+++ b/Outputs/PtX_demand_LU.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K37"/>
+  <dimension ref="A1:K43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -488,32 +488,32 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Hydrogen</t>
+          <t>Power</t>
         </is>
       </c>
       <c r="B2" t="n">
         <v>2030</v>
       </c>
-      <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="n">
-        <v>5.283656111244014e-05</v>
-      </c>
+      <c r="C2" t="n">
+        <v>0.006580790760876854</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.0007351002290916817</v>
+      </c>
+      <c r="E2" t="n">
+        <v>5.022786824012664e-05</v>
+      </c>
+      <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr"/>
-      <c r="H2" t="n">
-        <v>2.316635748153443e-10</v>
-      </c>
-      <c r="I2" t="n">
-        <v>2.459863587056758e-05</v>
-      </c>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Methanol</t>
+          <t>Hydrogen</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -522,17 +522,23 @@
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
+      <c r="F3" t="n">
+        <v>5.283656111244014e-05</v>
+      </c>
       <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
+      <c r="H3" t="n">
+        <v>2.316635748153443e-10</v>
+      </c>
+      <c r="I3" t="n">
+        <v>2.459863587056758e-05</v>
+      </c>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Ammonia</t>
+          <t>Methanol</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -551,7 +557,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Synthetic Gases</t>
+          <t>Ammonia</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -570,7 +576,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Biogenic Gases</t>
+          <t>Synthetic Gases</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -578,24 +584,18 @@
       </c>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr"/>
-      <c r="E6" t="n">
-        <v>0.0002070302133370287</v>
-      </c>
-      <c r="F6" t="n">
-        <v>1.616663178346188e-05</v>
-      </c>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr"/>
-      <c r="I6" t="n">
-        <v>4.303970734896349e-06</v>
-      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Fossil Gases</t>
+          <t>Biogenic Gases</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -603,14 +603,16 @@
       </c>
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
+      <c r="E7" t="n">
+        <v>0.0002070302133370287</v>
+      </c>
       <c r="F7" t="n">
-        <v>0.0002034442821474712</v>
+        <v>1.616663178346188e-05</v>
       </c>
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="n">
-        <v>1.806983956695509e-05</v>
+        <v>4.303970734896349e-06</v>
       </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
@@ -618,7 +620,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Synthetic Liquids</t>
+          <t>Fossil Gases</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -627,17 +629,21 @@
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
+      <c r="F8" t="n">
+        <v>0.0002034442821474712</v>
+      </c>
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
+      <c r="I8" t="n">
+        <v>1.806983956695509e-05</v>
+      </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Biogenic Liquids</t>
+          <t>Synthetic Liquids</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -646,29 +652,17 @@
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>
-      <c r="F9" t="n">
-        <v>0.0009583835277984215</v>
-      </c>
-      <c r="G9" t="n">
-        <v>5.625438470382552e-06</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0.0006338538975374</v>
-      </c>
-      <c r="I9" t="n">
-        <v>0.0008562968738091</v>
-      </c>
-      <c r="J9" t="n">
-        <v>3.332508913526928e-06</v>
-      </c>
-      <c r="K9" t="n">
-        <v>1.782381275225177e-05</v>
-      </c>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Fossil Liquids</t>
+          <t>Biogenic Liquids</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -678,28 +672,28 @@
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="n">
-        <v>0.009451835382458173</v>
+        <v>0.0009583835277984215</v>
       </c>
       <c r="G10" t="n">
-        <v>3.961831351454017e-05</v>
+        <v>5.625438470382552e-06</v>
       </c>
       <c r="H10" t="n">
-        <v>0.0057930828534679</v>
+        <v>0.0006338538975374</v>
       </c>
       <c r="I10" t="n">
-        <v>0.005393546397117</v>
+        <v>0.0008562968738091</v>
       </c>
       <c r="J10" t="n">
-        <v>2.017168346457447e-05</v>
+        <v>3.332508913526928e-06</v>
       </c>
       <c r="K10" t="n">
-        <v>0.0001274279191674</v>
+        <v>1.782381275225177e-05</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Biomass [Solid]</t>
+          <t>Fossil Liquids</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -707,20 +701,30 @@
       </c>
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr"/>
-      <c r="E11" t="n">
-        <v>0.0008830572976137143</v>
-      </c>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="n">
+        <v>0.009451835382458173</v>
+      </c>
+      <c r="G11" t="n">
+        <v>3.961831351454017e-05</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.0057930828534679</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0.005393546397117</v>
+      </c>
+      <c r="J11" t="n">
+        <v>2.017168346457447e-05</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0.0001274279191674</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Renewable Energy Carrier</t>
+          <t>Biomass [Solid]</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -729,7 +733,7 @@
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="n">
-        <v>8.694738566017942e-05</v>
+        <v>0.0008830572976137143</v>
       </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr"/>
@@ -741,7 +745,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Overall Demand</t>
+          <t>Fossil Rest</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -750,83 +754,91 @@
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="n">
-        <v>0.001177034896610922</v>
-      </c>
-      <c r="F13" t="n">
-        <v>0.01068266638529997</v>
-      </c>
-      <c r="G13" t="n">
-        <v>4.524375198492272e-05</v>
-      </c>
-      <c r="H13" t="n">
-        <v>0.006426936982668875</v>
-      </c>
-      <c r="I13" t="n">
-        <v>0.006296815717098519</v>
-      </c>
-      <c r="J13" t="n">
-        <v>2.35041923781014e-05</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0.0001452517319196518</v>
-      </c>
+        <v>0.002645798390974873</v>
+      </c>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Hydrogen</t>
+          <t>Renewable Energy Carrier</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2040</v>
+        <v>2030</v>
       </c>
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr"/>
-      <c r="F14" t="n">
-        <v>0.0002538681704911405</v>
-      </c>
+      <c r="E14" t="n">
+        <v>8.694738566017942e-05</v>
+      </c>
+      <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr"/>
-      <c r="H14" t="n">
-        <v>1.939279995423251e-08</v>
-      </c>
-      <c r="I14" t="n">
-        <v>3.554840186828434e-05</v>
-      </c>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Methanol</t>
+          <t>Overall Demand</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2040</v>
-      </c>
-      <c r="C15" t="inlineStr"/>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr"/>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr"/>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
+        <v>2030</v>
+      </c>
+      <c r="C15" t="n">
+        <v>0.006580790760876854</v>
+      </c>
+      <c r="D15" t="n">
+        <v>0.0007351002290916817</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0.003873061155825922</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0.01068266638529997</v>
+      </c>
+      <c r="G15" t="n">
+        <v>4.524375198492272e-05</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0.006426936982668875</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0.006296815717098519</v>
+      </c>
+      <c r="J15" t="n">
+        <v>2.35041923781014e-05</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0.0001452517319196518</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Ammonia</t>
+          <t>Power</t>
         </is>
       </c>
       <c r="B16" t="n">
         <v>2040</v>
       </c>
-      <c r="C16" t="inlineStr"/>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr"/>
+      <c r="C16" t="n">
+        <v>0.00651663144646848</v>
+      </c>
+      <c r="D16" t="n">
+        <v>0.0005215980805468769</v>
+      </c>
+      <c r="E16" t="n">
+        <v>1.459297267677524e-05</v>
+      </c>
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr"/>
@@ -837,7 +849,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Synthetic Gases</t>
+          <t>Hydrogen</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -847,12 +859,14 @@
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr"/>
       <c r="F17" t="n">
-        <v>9.296301033643273e-11</v>
+        <v>0.0002538681704911405</v>
       </c>
       <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr"/>
+      <c r="H17" t="n">
+        <v>1.939279995423251e-08</v>
+      </c>
       <c r="I17" t="n">
-        <v>1.094815672177908e-11</v>
+        <v>3.554840186828434e-05</v>
       </c>
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
@@ -860,7 +874,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Biogenic Gases</t>
+          <t>Methanol</t>
         </is>
       </c>
       <c r="B18" t="n">
@@ -868,24 +882,18 @@
       </c>
       <c r="C18" t="inlineStr"/>
       <c r="D18" t="inlineStr"/>
-      <c r="E18" t="n">
-        <v>0.0008090434386974429</v>
-      </c>
-      <c r="F18" t="n">
-        <v>1.988819906160648e-05</v>
-      </c>
+      <c r="E18" t="inlineStr"/>
+      <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr"/>
-      <c r="I18" t="n">
-        <v>7.533376086321518e-06</v>
-      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Fossil Gases</t>
+          <t>Ammonia</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -894,21 +902,17 @@
       <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr"/>
-      <c r="F19" t="n">
-        <v>0.0001102345306729826</v>
-      </c>
+      <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr"/>
-      <c r="I19" t="n">
-        <v>1.913760421229235e-05</v>
-      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Synthetic Liquids</t>
+          <t>Synthetic Gases</t>
         </is>
       </c>
       <c r="B20" t="n">
@@ -917,17 +921,21 @@
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr"/>
-      <c r="F20" t="inlineStr"/>
+      <c r="F20" t="n">
+        <v>9.296301033643273e-11</v>
+      </c>
       <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr"/>
-      <c r="I20" t="inlineStr"/>
+      <c r="I20" t="n">
+        <v>1.094815672177908e-11</v>
+      </c>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Biogenic Liquids</t>
+          <t>Biogenic Gases</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -935,30 +943,24 @@
       </c>
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr"/>
+      <c r="E21" t="n">
+        <v>0.0008090434386974429</v>
+      </c>
       <c r="F21" t="n">
-        <v>0.0004169401728129474</v>
-      </c>
-      <c r="G21" t="n">
-        <v>9.170392762475309e-06</v>
-      </c>
-      <c r="H21" t="n">
-        <v>0.0007716265368593</v>
-      </c>
+        <v>1.988819906160648e-05</v>
+      </c>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr"/>
       <c r="I21" t="n">
-        <v>0.0005640913233956999</v>
-      </c>
-      <c r="J21" t="n">
-        <v>4.048457469194271e-06</v>
-      </c>
-      <c r="K21" t="n">
-        <v>2.340641662853338e-05</v>
-      </c>
+        <v>7.533376086321518e-06</v>
+      </c>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Fossil Liquids</t>
+          <t>Fossil Gases</t>
         </is>
       </c>
       <c r="B22" t="n">
@@ -968,28 +970,20 @@
       <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr"/>
       <c r="F22" t="n">
-        <v>0.002578360594290656</v>
-      </c>
-      <c r="G22" t="n">
-        <v>4.259188969353732e-05</v>
-      </c>
-      <c r="H22" t="n">
-        <v>0.0054617946555969</v>
-      </c>
+        <v>0.0001102345306729826</v>
+      </c>
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="inlineStr"/>
       <c r="I22" t="n">
-        <v>0.0024037440514657</v>
-      </c>
-      <c r="J22" t="n">
-        <v>1.79005644140739e-05</v>
-      </c>
-      <c r="K22" t="n">
-        <v>0.0001124321287735</v>
-      </c>
+        <v>1.913760421229235e-05</v>
+      </c>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Biomass [Solid]</t>
+          <t>Synthetic Liquids</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -997,9 +991,7 @@
       </c>
       <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr"/>
-      <c r="E23" t="n">
-        <v>0.0009767952413055328</v>
-      </c>
+      <c r="E23" t="inlineStr"/>
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr"/>
       <c r="H23" t="inlineStr"/>
@@ -1010,7 +1002,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Renewable Energy Carrier</t>
+          <t>Biogenic Liquids</t>
         </is>
       </c>
       <c r="B24" t="n">
@@ -1018,20 +1010,30 @@
       </c>
       <c r="C24" t="inlineStr"/>
       <c r="D24" t="inlineStr"/>
-      <c r="E24" t="n">
-        <v>0.0003568693389818933</v>
-      </c>
-      <c r="F24" t="inlineStr"/>
-      <c r="G24" t="inlineStr"/>
-      <c r="H24" t="inlineStr"/>
-      <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
+      <c r="E24" t="inlineStr"/>
+      <c r="F24" t="n">
+        <v>0.0004169401728129474</v>
+      </c>
+      <c r="G24" t="n">
+        <v>9.170392762475309e-06</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0.0007716265368593</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0.0005640913233956999</v>
+      </c>
+      <c r="J24" t="n">
+        <v>4.048457469194271e-06</v>
+      </c>
+      <c r="K24" t="n">
+        <v>2.340641662853338e-05</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Overall Demand</t>
+          <t>Fossil Liquids</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -1039,65 +1041,61 @@
       </c>
       <c r="C25" t="inlineStr"/>
       <c r="D25" t="inlineStr"/>
-      <c r="E25" t="n">
-        <v>0.002142708018984869</v>
-      </c>
+      <c r="E25" t="inlineStr"/>
       <c r="F25" t="n">
-        <v>0.003379291760292343</v>
+        <v>0.002578360594290656</v>
       </c>
       <c r="G25" t="n">
-        <v>5.176228245601263e-05</v>
+        <v>4.259188969353732e-05</v>
       </c>
       <c r="H25" t="n">
-        <v>0.006233440585256155</v>
+        <v>0.0054617946555969</v>
       </c>
       <c r="I25" t="n">
-        <v>0.003030054767976455</v>
+        <v>0.0024037440514657</v>
       </c>
       <c r="J25" t="n">
-        <v>2.194902188326818e-05</v>
+        <v>1.79005644140739e-05</v>
       </c>
       <c r="K25" t="n">
-        <v>0.0001358385454020334</v>
+        <v>0.0001124321287735</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Hydrogen</t>
+          <t>Biomass [Solid]</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>2050</v>
+        <v>2040</v>
       </c>
       <c r="C26" t="inlineStr"/>
       <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr"/>
-      <c r="F26" t="n">
-        <v>0.0003521444160408327</v>
-      </c>
+      <c r="E26" t="n">
+        <v>0.0009767952413055328</v>
+      </c>
+      <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr"/>
-      <c r="H26" t="n">
-        <v>3.286923386352513e-08</v>
-      </c>
-      <c r="I26" t="n">
-        <v>5.661741231548529e-05</v>
-      </c>
+      <c r="H26" t="inlineStr"/>
+      <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Methanol</t>
+          <t>Fossil Rest</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>2050</v>
+        <v>2040</v>
       </c>
       <c r="C27" t="inlineStr"/>
       <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr"/>
+      <c r="E27" t="n">
+        <v>0.001748869166519004</v>
+      </c>
       <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr"/>
       <c r="H27" t="inlineStr"/>
@@ -1108,15 +1106,17 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Ammonia</t>
+          <t>Renewable Energy Carrier</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>2050</v>
+        <v>2040</v>
       </c>
       <c r="C28" t="inlineStr"/>
       <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr"/>
+      <c r="E28" t="n">
+        <v>0.0003568693389818933</v>
+      </c>
       <c r="F28" t="inlineStr"/>
       <c r="G28" t="inlineStr"/>
       <c r="H28" t="inlineStr"/>
@@ -1127,55 +1127,67 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Synthetic Gases</t>
+          <t>Overall Demand</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>2050</v>
-      </c>
-      <c r="C29" t="inlineStr"/>
-      <c r="D29" t="inlineStr"/>
-      <c r="E29" t="inlineStr"/>
+        <v>2040</v>
+      </c>
+      <c r="C29" t="n">
+        <v>0.00651663144646848</v>
+      </c>
+      <c r="D29" t="n">
+        <v>0.0005215980805468769</v>
+      </c>
+      <c r="E29" t="n">
+        <v>0.003906170158180649</v>
+      </c>
       <c r="F29" t="n">
-        <v>8.70044268609369e-10</v>
-      </c>
-      <c r="G29" t="inlineStr"/>
-      <c r="H29" t="inlineStr"/>
+        <v>0.003379291760292343</v>
+      </c>
+      <c r="G29" t="n">
+        <v>5.176228245601263e-05</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0.006233440585256155</v>
+      </c>
       <c r="I29" t="n">
-        <v>2.68551980919303e-10</v>
-      </c>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
+        <v>0.003030054767976455</v>
+      </c>
+      <c r="J29" t="n">
+        <v>2.194902188326818e-05</v>
+      </c>
+      <c r="K29" t="n">
+        <v>0.0001358385454020334</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Biogenic Gases</t>
+          <t>Power</t>
         </is>
       </c>
       <c r="B30" t="n">
         <v>2050</v>
       </c>
-      <c r="C30" t="inlineStr"/>
-      <c r="D30" t="inlineStr"/>
-      <c r="E30" t="n">
-        <v>0.001955551764325928</v>
-      </c>
-      <c r="F30" t="n">
-        <v>3.406830721744977e-06</v>
-      </c>
+      <c r="C30" t="n">
+        <v>0.006439082511987116</v>
+      </c>
+      <c r="D30" t="n">
+        <v>0.0002635394606597107</v>
+      </c>
+      <c r="E30" t="inlineStr"/>
+      <c r="F30" t="inlineStr"/>
       <c r="G30" t="inlineStr"/>
       <c r="H30" t="inlineStr"/>
-      <c r="I30" t="n">
-        <v>2.173206784143539e-06</v>
-      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Fossil Gases</t>
+          <t>Hydrogen</t>
         </is>
       </c>
       <c r="B31" t="n">
@@ -1185,12 +1197,14 @@
       <c r="D31" t="inlineStr"/>
       <c r="E31" t="inlineStr"/>
       <c r="F31" t="n">
-        <v>6.883362693042184e-06</v>
+        <v>0.0003521444160408327</v>
       </c>
       <c r="G31" t="inlineStr"/>
-      <c r="H31" t="inlineStr"/>
+      <c r="H31" t="n">
+        <v>3.286923386352513e-08</v>
+      </c>
       <c r="I31" t="n">
-        <v>7.190442366028786e-06</v>
+        <v>5.661741231548529e-05</v>
       </c>
       <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
@@ -1198,7 +1212,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Synthetic Liquids</t>
+          <t>Methanol</t>
         </is>
       </c>
       <c r="B32" t="n">
@@ -1207,29 +1221,17 @@
       <c r="C32" t="inlineStr"/>
       <c r="D32" t="inlineStr"/>
       <c r="E32" t="inlineStr"/>
-      <c r="F32" t="n">
-        <v>2.22160304401638e-12</v>
-      </c>
-      <c r="G32" t="n">
-        <v>3.376959998382159e-13</v>
-      </c>
-      <c r="H32" t="n">
-        <v>2.97286737647877e-11</v>
-      </c>
-      <c r="I32" t="n">
-        <v>9.438632566327578e-12</v>
-      </c>
-      <c r="J32" t="n">
-        <v>2.772717958064315e-14</v>
-      </c>
-      <c r="K32" t="n">
-        <v>3.94304446365687e-12</v>
-      </c>
+      <c r="F32" t="inlineStr"/>
+      <c r="G32" t="inlineStr"/>
+      <c r="H32" t="inlineStr"/>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Biogenic Liquids</t>
+          <t>Ammonia</t>
         </is>
       </c>
       <c r="B33" t="n">
@@ -1238,29 +1240,17 @@
       <c r="C33" t="inlineStr"/>
       <c r="D33" t="inlineStr"/>
       <c r="E33" t="inlineStr"/>
-      <c r="F33" t="n">
-        <v>4.141827709932304e-05</v>
-      </c>
-      <c r="G33" t="n">
-        <v>1.63858818076062e-05</v>
-      </c>
-      <c r="H33" t="n">
-        <v>0.0010106645142242</v>
-      </c>
-      <c r="I33" t="n">
-        <v>0.000145301372805227</v>
-      </c>
-      <c r="J33" t="n">
-        <v>5.206957399277256e-06</v>
-      </c>
-      <c r="K33" t="n">
-        <v>3.178818888705797e-05</v>
-      </c>
+      <c r="F33" t="inlineStr"/>
+      <c r="G33" t="inlineStr"/>
+      <c r="H33" t="inlineStr"/>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Fossil Liquids</t>
+          <t>Synthetic Gases</t>
         </is>
       </c>
       <c r="B34" t="n">
@@ -1270,28 +1260,20 @@
       <c r="D34" t="inlineStr"/>
       <c r="E34" t="inlineStr"/>
       <c r="F34" t="n">
-        <v>0.0001449010494921588</v>
-      </c>
-      <c r="G34" t="n">
-        <v>3.841608072198006e-05</v>
-      </c>
-      <c r="H34" t="n">
-        <v>0.0049531446154624</v>
-      </c>
+        <v>8.70044268609369e-10</v>
+      </c>
+      <c r="G34" t="inlineStr"/>
+      <c r="H34" t="inlineStr"/>
       <c r="I34" t="n">
-        <v>0.0004293438138343</v>
-      </c>
-      <c r="J34" t="n">
-        <v>1.54079268861911e-05</v>
-      </c>
-      <c r="K34" t="n">
-        <v>9.227971885962604e-05</v>
-      </c>
+        <v>2.68551980919303e-10</v>
+      </c>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Biomass [Solid]</t>
+          <t>Biogenic Gases</t>
         </is>
       </c>
       <c r="B35" t="n">
@@ -1300,19 +1282,23 @@
       <c r="C35" t="inlineStr"/>
       <c r="D35" t="inlineStr"/>
       <c r="E35" t="n">
-        <v>0.001096317097920804</v>
-      </c>
-      <c r="F35" t="inlineStr"/>
+        <v>0.001955551764325928</v>
+      </c>
+      <c r="F35" t="n">
+        <v>3.406830721744977e-06</v>
+      </c>
       <c r="G35" t="inlineStr"/>
       <c r="H35" t="inlineStr"/>
-      <c r="I35" t="inlineStr"/>
+      <c r="I35" t="n">
+        <v>2.173206784143539e-06</v>
+      </c>
       <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Renewable Energy Carrier</t>
+          <t>Fossil Gases</t>
         </is>
       </c>
       <c r="B36" t="n">
@@ -1320,20 +1306,22 @@
       </c>
       <c r="C36" t="inlineStr"/>
       <c r="D36" t="inlineStr"/>
-      <c r="E36" t="n">
-        <v>0.0009155415375954781</v>
-      </c>
-      <c r="F36" t="inlineStr"/>
+      <c r="E36" t="inlineStr"/>
+      <c r="F36" t="n">
+        <v>6.883362693042184e-06</v>
+      </c>
       <c r="G36" t="inlineStr"/>
       <c r="H36" t="inlineStr"/>
-      <c r="I36" t="inlineStr"/>
+      <c r="I36" t="n">
+        <v>7.190442366028786e-06</v>
+      </c>
       <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Overall Demand</t>
+          <t>Synthetic Liquids</t>
         </is>
       </c>
       <c r="B37" t="n">
@@ -1341,25 +1329,183 @@
       </c>
       <c r="C37" t="inlineStr"/>
       <c r="D37" t="inlineStr"/>
-      <c r="E37" t="n">
+      <c r="E37" t="inlineStr"/>
+      <c r="F37" t="n">
+        <v>2.22160304401638e-12</v>
+      </c>
+      <c r="G37" t="n">
+        <v>3.376959998382159e-13</v>
+      </c>
+      <c r="H37" t="n">
+        <v>2.97286737647877e-11</v>
+      </c>
+      <c r="I37" t="n">
+        <v>9.438632566327578e-12</v>
+      </c>
+      <c r="J37" t="n">
+        <v>2.772717958064315e-14</v>
+      </c>
+      <c r="K37" t="n">
+        <v>3.94304446365687e-12</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Biogenic Liquids</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>2050</v>
+      </c>
+      <c r="C38" t="inlineStr"/>
+      <c r="D38" t="inlineStr"/>
+      <c r="E38" t="inlineStr"/>
+      <c r="F38" t="n">
+        <v>4.141827709932304e-05</v>
+      </c>
+      <c r="G38" t="n">
+        <v>1.63858818076062e-05</v>
+      </c>
+      <c r="H38" t="n">
+        <v>0.0010106645142242</v>
+      </c>
+      <c r="I38" t="n">
+        <v>0.000145301372805227</v>
+      </c>
+      <c r="J38" t="n">
+        <v>5.206957399277256e-06</v>
+      </c>
+      <c r="K38" t="n">
+        <v>3.178818888705797e-05</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Fossil Liquids</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>2050</v>
+      </c>
+      <c r="C39" t="inlineStr"/>
+      <c r="D39" t="inlineStr"/>
+      <c r="E39" t="inlineStr"/>
+      <c r="F39" t="n">
+        <v>0.0001449010494921588</v>
+      </c>
+      <c r="G39" t="n">
+        <v>3.841608072198006e-05</v>
+      </c>
+      <c r="H39" t="n">
+        <v>0.0049531446154624</v>
+      </c>
+      <c r="I39" t="n">
+        <v>0.0004293438138343</v>
+      </c>
+      <c r="J39" t="n">
+        <v>1.54079268861911e-05</v>
+      </c>
+      <c r="K39" t="n">
+        <v>9.227971885962604e-05</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Biomass [Solid]</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>2050</v>
+      </c>
+      <c r="C40" t="inlineStr"/>
+      <c r="D40" t="inlineStr"/>
+      <c r="E40" t="n">
+        <v>0.001096317097920804</v>
+      </c>
+      <c r="F40" t="inlineStr"/>
+      <c r="G40" t="inlineStr"/>
+      <c r="H40" t="inlineStr"/>
+      <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Fossil Rest</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>2050</v>
+      </c>
+      <c r="C41" t="inlineStr"/>
+      <c r="D41" t="inlineStr"/>
+      <c r="E41" t="inlineStr"/>
+      <c r="F41" t="inlineStr"/>
+      <c r="G41" t="inlineStr"/>
+      <c r="H41" t="inlineStr"/>
+      <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Renewable Energy Carrier</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>2050</v>
+      </c>
+      <c r="C42" t="inlineStr"/>
+      <c r="D42" t="inlineStr"/>
+      <c r="E42" t="n">
+        <v>0.0009155415375954781</v>
+      </c>
+      <c r="F42" t="inlineStr"/>
+      <c r="G42" t="inlineStr"/>
+      <c r="H42" t="inlineStr"/>
+      <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Overall Demand</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>2050</v>
+      </c>
+      <c r="C43" t="n">
+        <v>0.006439082511987116</v>
+      </c>
+      <c r="D43" t="n">
+        <v>0.0002635394606597107</v>
+      </c>
+      <c r="E43" t="n">
         <v>0.003967410399842211</v>
       </c>
-      <c r="F37" t="n">
+      <c r="F43" t="n">
         <v>0.0005487548083129735</v>
       </c>
-      <c r="G37" t="n">
+      <c r="G43" t="n">
         <v>5.480196286728226e-05</v>
       </c>
-      <c r="H37" t="n">
+      <c r="H43" t="n">
         <v>0.005963842028649137</v>
       </c>
-      <c r="I37" t="n">
+      <c r="I43" t="n">
         <v>0.000640626526095798</v>
       </c>
-      <c r="J37" t="n">
+      <c r="J43" t="n">
         <v>2.061488431319554e-05</v>
       </c>
-      <c r="K37" t="n">
+      <c r="K43" t="n">
         <v>0.0001240679116897285</v>
       </c>
     </row>

--- a/Outputs/PtX_demand_LU.xlsx
+++ b/Outputs/PtX_demand_LU.xlsx
@@ -503,11 +503,19 @@
       <c r="E2" t="n">
         <v>5.022786824012664e-05</v>
       </c>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
+      <c r="F2" t="n">
+        <v>0.001155751075605885</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.0002277903604785</v>
+      </c>
       <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
+      <c r="I2" t="n">
+        <v>0.0003791725137432</v>
+      </c>
+      <c r="J2" t="n">
+        <v>3.01996861114036e-05</v>
+      </c>
       <c r="K2" t="inlineStr"/>
     </row>
     <row r="3">
@@ -724,7 +732,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Biomass [Solid]</t>
+          <t>Fossil Residuals</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -733,7 +741,7 @@
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="n">
-        <v>0.0008830572976137143</v>
+        <v>0.002645798390974873</v>
       </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr"/>
@@ -745,7 +753,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Fossil Rest</t>
+          <t>Biomass [Solid]</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -754,7 +762,7 @@
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="n">
-        <v>0.002645798390974873</v>
+        <v>0.0008830572976137143</v>
       </c>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr"/>
@@ -803,19 +811,19 @@
         <v>0.003873061155825922</v>
       </c>
       <c r="F15" t="n">
-        <v>0.01068266638529997</v>
+        <v>0.01183841746090585</v>
       </c>
       <c r="G15" t="n">
-        <v>4.524375198492272e-05</v>
+        <v>0.0002730341124634227</v>
       </c>
       <c r="H15" t="n">
         <v>0.006426936982668875</v>
       </c>
       <c r="I15" t="n">
-        <v>0.006296815717098519</v>
+        <v>0.006675988230841719</v>
       </c>
       <c r="J15" t="n">
-        <v>2.35041923781014e-05</v>
+        <v>5.3703878489505e-05</v>
       </c>
       <c r="K15" t="n">
         <v>0.0001452517319196518</v>
@@ -839,11 +847,19 @@
       <c r="E16" t="n">
         <v>1.459297267677524e-05</v>
       </c>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr"/>
+      <c r="F16" t="n">
+        <v>0.003288198876422079</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0.000267332998628</v>
+      </c>
       <c r="H16" t="inlineStr"/>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
+      <c r="I16" t="n">
+        <v>0.0012887433199403</v>
+      </c>
+      <c r="J16" t="n">
+        <v>2.978390853286915e-05</v>
+      </c>
       <c r="K16" t="inlineStr"/>
     </row>
     <row r="17">
@@ -1064,7 +1080,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Biomass [Solid]</t>
+          <t>Fossil Residuals</t>
         </is>
       </c>
       <c r="B26" t="n">
@@ -1073,7 +1089,7 @@
       <c r="C26" t="inlineStr"/>
       <c r="D26" t="inlineStr"/>
       <c r="E26" t="n">
-        <v>0.0009767952413055328</v>
+        <v>0.001748869166519004</v>
       </c>
       <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr"/>
@@ -1085,7 +1101,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Fossil Rest</t>
+          <t>Biomass [Solid]</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -1094,7 +1110,7 @@
       <c r="C27" t="inlineStr"/>
       <c r="D27" t="inlineStr"/>
       <c r="E27" t="n">
-        <v>0.001748869166519004</v>
+        <v>0.0009767952413055328</v>
       </c>
       <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr"/>
@@ -1140,22 +1156,22 @@
         <v>0.0005215980805468769</v>
       </c>
       <c r="E29" t="n">
-        <v>0.003906170158180649</v>
+        <v>0.003906170158180648</v>
       </c>
       <c r="F29" t="n">
-        <v>0.003379291760292343</v>
+        <v>0.006667490636714422</v>
       </c>
       <c r="G29" t="n">
-        <v>5.176228245601263e-05</v>
+        <v>0.0003190952810840127</v>
       </c>
       <c r="H29" t="n">
         <v>0.006233440585256155</v>
       </c>
       <c r="I29" t="n">
-        <v>0.003030054767976455</v>
+        <v>0.004318798087916755</v>
       </c>
       <c r="J29" t="n">
-        <v>2.194902188326818e-05</v>
+        <v>5.173293041613732e-05</v>
       </c>
       <c r="K29" t="n">
         <v>0.0001358385454020334</v>
@@ -1177,11 +1193,19 @@
         <v>0.0002635394606597107</v>
       </c>
       <c r="E30" t="inlineStr"/>
-      <c r="F30" t="inlineStr"/>
-      <c r="G30" t="inlineStr"/>
+      <c r="F30" t="n">
+        <v>0.003833076371002123</v>
+      </c>
+      <c r="G30" t="n">
+        <v>0.0003002133950296</v>
+      </c>
       <c r="H30" t="inlineStr"/>
-      <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
+      <c r="I30" t="n">
+        <v>0.0019022272163612</v>
+      </c>
+      <c r="J30" t="n">
+        <v>3.041902240645558e-05</v>
+      </c>
       <c r="K30" t="inlineStr"/>
     </row>
     <row r="31">
@@ -1414,7 +1438,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Biomass [Solid]</t>
+          <t>Fossil Residuals</t>
         </is>
       </c>
       <c r="B40" t="n">
@@ -1422,9 +1446,7 @@
       </c>
       <c r="C40" t="inlineStr"/>
       <c r="D40" t="inlineStr"/>
-      <c r="E40" t="n">
-        <v>0.001096317097920804</v>
-      </c>
+      <c r="E40" t="inlineStr"/>
       <c r="F40" t="inlineStr"/>
       <c r="G40" t="inlineStr"/>
       <c r="H40" t="inlineStr"/>
@@ -1435,7 +1457,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Fossil Rest</t>
+          <t>Biomass [Solid]</t>
         </is>
       </c>
       <c r="B41" t="n">
@@ -1443,7 +1465,9 @@
       </c>
       <c r="C41" t="inlineStr"/>
       <c r="D41" t="inlineStr"/>
-      <c r="E41" t="inlineStr"/>
+      <c r="E41" t="n">
+        <v>0.001096317097920804</v>
+      </c>
       <c r="F41" t="inlineStr"/>
       <c r="G41" t="inlineStr"/>
       <c r="H41" t="inlineStr"/>
@@ -1491,19 +1515,19 @@
         <v>0.003967410399842211</v>
       </c>
       <c r="F43" t="n">
-        <v>0.0005487548083129735</v>
+        <v>0.004381831179315096</v>
       </c>
       <c r="G43" t="n">
-        <v>5.480196286728226e-05</v>
+        <v>0.0003550153578968822</v>
       </c>
       <c r="H43" t="n">
         <v>0.005963842028649137</v>
       </c>
       <c r="I43" t="n">
-        <v>0.000640626526095798</v>
+        <v>0.002542853742456998</v>
       </c>
       <c r="J43" t="n">
-        <v>2.061488431319554e-05</v>
+        <v>5.103390671965111e-05</v>
       </c>
       <c r="K43" t="n">
         <v>0.0001240679116897285</v>
